--- a/JD换电柜终端_20261028提测功能测试用例.xlsx
+++ b/JD换电柜终端_20261028提测功能测试用例.xlsx
@@ -2524,18 +2524,115 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">保持命令电流 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">&gt; 0
-2. </t>
+      <t xml:space="preserve">命令电流 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&gt; 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持续充电，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保持不变
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续保持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟无变化
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">记录告警产生时刻与内容
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
     </r>
     <r>
       <rPr>
@@ -2563,50 +2660,14 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连续 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分钟无变化
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">观察告警</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">累计满 30 分钟产生 55 并上报</t>
+      <t xml:space="preserve">变化后再观察消除</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 累计满 30 分钟时产生 1 条告警 55 并上报，仓号正确
+2. 未满 30 分钟前不产生 55
+3. 告警产生时刻与 SOC 开始不变的时刻相差 30 分钟（允许 P-08 计时精度）
+4. SOC 变化后告警消除，平台状态同步</t>
   </si>
   <si>
     <t xml:space="preserve">【告警55】-命令电流为 0 且 BMS 充电时 SOC 上升不报</t>
@@ -7151,7 +7212,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">先制造总功率不足
+      <t xml:space="preserve">满仓并发充电，限制总输入功率制造功率不足
 </t>
     </r>
     <r>
@@ -7171,7 +7232,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">解除限制使功率充足
+      <t xml:space="preserve">逐仓测量电流并记录限流期间的分配
 </t>
     </r>
     <r>
@@ -7191,11 +7252,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">观察各仓电流</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">各仓平滑回到满需求，无过冲/保护</t>
+      <t xml:space="preserve">解除限制使总功率充足
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再逐仓测量电流</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 限流期间各仓电流 ≥ P-14，无 0 电流仓
+2. 解除限制后各仓电流上升至 ≥ P-13（满需求），无仓停留在涓流
+3. 恢复过程无过冲、无过流保护动作、无异响
+4. 柜总功率始终 ≤ P-15</t>
   </si>
   <si>
     <t xml:space="preserve">【功率分配】-分配切换时电流无跳变不触发保护</t>
@@ -7442,7 +7526,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">升级中断网
+      <t xml:space="preserve">发起升级，在下载阶段断开网络
 </t>
     </r>
     <r>
@@ -7462,6 +7546,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">保持断网 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">恢复网络
 </t>
     </r>
@@ -7473,20 +7596,23 @@
         <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">观察重试与升级结果</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">按重试机制恢复，升级完成或明确失败；状态在平台可见</t>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">观察重试次数、升级结果与平台状态</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 断网期间升级进入重试/等待，不误报成功
+2. 恢复网络后按 P-16 的重试机制继续，重试次数 ≤3
+3. 升级最终成功或明确失败（失败时平台可见失败原因）
+4. 无重复升级任务、设备不砖机</t>
   </si>
   <si>
     <t xml:space="preserve">【去清BMS历史】-关门不再清除 BMS 历史</t>
@@ -7626,7 +7752,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">记录升级前历史
+      <t xml:space="preserve">记录升级前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">历史条数与内容
 </t>
     </r>
     <r>
@@ -7666,11 +7811,53 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">对比历史</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">升级不清除 BMS 历史，记录连续</t>
+      <t xml:space="preserve">升级后对比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">历史
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再开关一次柜门后对比</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 升级后 BMS 历史条数与内容与升级前一致（差异条数为 0）
+2. 升级动作本身不清除历史
+3. 开关门后历史继续累计，不重置
+4. 终端日志无清除 BMS 历史动作</t>
   </si>
   <si>
     <t xml:space="preserve">【去清BMS历史】-连续多次开关门历史持续累计</t>
@@ -7903,7 +8090,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">断网 </t>
+      <t xml:space="preserve">断开网络 </t>
     </r>
     <r>
       <rPr>
@@ -7962,11 +8149,53 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">观察连接数、会话、补报</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">单次连接成功，无重复连接/多会话；数据与告警补报正常</t>
+      <t xml:space="preserve">观察连接建立次数与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">MQTT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会话数
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">观察断网期间的数据与告警是否补报</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 恢复后仅建立 1 次连接、1 个会话，无重复连接
+2. 不出现连接风暴（5 分钟内重连次数 ≤ P-18）
+3. 断网期间产生的告警与定时数据在恢复后补报，无丢失、无重复
+4. 平台侧会话数不出现多实例</t>
   </si>
   <si>
     <t xml:space="preserve">【网络优化】-长时间断网按退避重试无连接风暴</t>
@@ -8089,7 +8318,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">断网期间产生告警并恢复
+      <t xml:space="preserve">断网期间注入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">故障产生告警，再恢复故障使告警消除
 </t>
     </r>
     <r>
@@ -8109,7 +8357,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">网络恢复
+      <t xml:space="preserve">恢复网络
 </t>
     </r>
     <r>
@@ -8129,12 +8377,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">查看平台最终状态</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">平台最终状态与终端一致，无丢失、无重复
-备注：ACK 异常依赖 BL-01</t>
+      <t xml:space="preserve">查看平台告警最终状态
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与终端本地状态对比</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 平台最终无该告警（已消除），无悬挂
+2. 平台不出现同码 2 条及以上记录
+3. 终端本地与平台状态一致
+4. 备注：ACK 丢失/重复场景依赖 BL-01，不在本条范围</t>
   </si>
   <si>
     <t xml:space="preserve">【升级告警抑制】-升级窗口起止边界的抑制范围</t>
@@ -8446,7 +8716,9 @@
     <t xml:space="preserve">JD_CAB_TER_058</t>
   </si>
   <si>
-    <t xml:space="preserve">可构造软件记录状态与门磁不一致（异常断电/升级后）</t>
+    <t xml:space="preserve">1. 可构造软件记录状态与门磁实际不一致（异常断电/升级后）
+2. 可重启终端
+3. 可同时查看门磁实际状态与平台状态</t>
   </si>
   <si>
     <r>
@@ -8506,12 +8778,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">查看平台与本地状态</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">以门磁实际状态为准，重启后自动纠正为“开”，无残留错误状态
-备注：若无法构造，用 SMK-02 覆盖并备注</t>
+      <t xml:space="preserve">查看平台与本地状态
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再次开合门验证纠正后行为</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 重启后以门磁实际状态为准，平台显示为“开”
+2. 无残留错误状态，与门磁实物一致
+3. 后续开合门状态正常跟随门磁
+4. 备注：异常场景若无法构造，改由 JD_CAB_TER_057 的重启一致性覆盖并在结果中注明</t>
   </si>
   <si>
     <t xml:space="preserve">物模型版本提升后版本号与字段正确（回归 JD_BMS_OTA_047/048）</t>
@@ -8954,6 +9248,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">命令电流 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&gt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">处于 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">0~95 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区间
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">使 </t>
     </r>
     <r>
@@ -8973,46 +9344,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">0~95 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区间下降并停滞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">保持 </t>
+      <t xml:space="preserve">在该区间下降并停滞 </t>
     </r>
     <r>
       <rPr>
@@ -9031,7 +9363,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分钟无变化
+      <t xml:space="preserve">分钟
 </t>
     </r>
     <r>
@@ -9051,11 +9383,52 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">观察告警</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">产生告警 55 并上报，含仓号</t>
+      <t xml:space="preserve">观察告警与仓号
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">变化后观察消除</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 累计满 30 分钟产生 1 条告警 55 并上报，含正确仓号
+2. 其他仓不产生 55
+3. SOC 变化后告警消除，平台状态同步</t>
   </si>
   <si>
     <t xml:space="preserve">告警55 恢复后消除上报（回归 JD_BMS_OTA_066/067/068）</t>
@@ -10527,7 +10900,9 @@
     <t xml:space="preserve">JD_CAB_TER_073</t>
   </si>
   <si>
-    <t xml:space="preserve">柜内有可升级电池，已获取升级包</t>
+    <t xml:space="preserve">1. 柜内有可升级电池
+2. 已获取升级包（版本号见 P-02）
+3. 平台可查看电池版本</t>
   </si>
   <si>
     <r>
@@ -10567,7 +10942,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">观察升级过程与结果
+      <t xml:space="preserve">观察升级过程状态（下发、传输、写入、校验）
 </t>
     </r>
     <r>
@@ -10587,12 +10962,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">查看电池版本</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">升级成功，电池版本更新为目标版本，过程状态在平台可见
-备注：升级包版本待填</t>
+      <t xml:space="preserve">查看电池版本
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">升级后执行一次充电与换电</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 升级成功，电池版本更新为 P-02 指定版本
+2. 升级过程各阶段状态在平台可见，无卡死
+3. 失败时明确上报失败原因，不误报成功
+4. 升级后电池可正常充电、可正常换出换入</t>
   </si>
   <si>
     <t xml:space="preserve">JD 国标电池 SN 正确上报</t>
@@ -12094,21 +12491,206 @@
     <t xml:space="preserve">P-26</t>
   </si>
   <si>
+    <t xml:space="preserve">柜温/环温短路与开路时上报的“柜高温告警”告警码及温度上报值定义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次改为有符号数后短路/开路上报柜高温告警</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待确认</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">柜温</t>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E55 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中“命令电流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">=0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">充电但 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期不变”的归属：上一版按累计（会报 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），本次新增“命令电流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未禁充暂停”与之重叠，需研发明确优先规则</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_026</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">影响预期判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阻塞</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">broker ACK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丢失</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">/</t>
     </r>
     <r>
@@ -12117,26 +12699,59 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">环温短路与开路时上报的“柜高温告警”告警码及温度上报值定义</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">延迟</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本次改为有符号数后短路</t>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重复的注入或抓取能力缺失</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">需研发/平台支持</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告警 51/54/102 无稳定触发手段（需研发提供触发方式）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未关闭则该组不可执行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">负温环境构造资源不足（无温箱/电阻箱）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冰袋/冷柜或传感器模拟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">22 </t>
     </r>
     <r>
       <rPr>
@@ -12144,22 +12759,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">开路上报柜高温告警</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">事项</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响用例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">待确认</t>
-  </si>
-  <si>
+      <t xml:space="preserve">种 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -12167,7 +12768,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">E55 </t>
+      <t xml:space="preserve">BMS </t>
     </r>
     <r>
       <rPr>
@@ -12175,7 +12776,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中“命令电流</t>
+      <t xml:space="preserve">故障逐 </t>
     </r>
     <r>
       <rPr>
@@ -12184,7 +12785,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">=0 </t>
+      <t xml:space="preserve">bit </t>
     </r>
     <r>
       <rPr>
@@ -12192,7 +12793,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">且 </t>
+      <t xml:space="preserve">注入能力未确认；与上一版 </t>
     </r>
     <r>
       <rPr>
@@ -12201,7 +12802,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BMS </t>
+      <t xml:space="preserve">49 </t>
     </r>
     <r>
       <rPr>
@@ -12209,258 +12810,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">充电但 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SOC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期不变”的归属：上一版按累计（会报 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），本次新增“命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未禁充暂停”与之重叠，需研发明确优先规则</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_017</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_026</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">影响预期判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阻塞</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">broker ACK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丢失</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">延迟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重复的注入或抓取能力缺失</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">需研发/平台支持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告警 51/54/102 无稳定触发手段（需研发提供触发方式）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未关闭则该组不可执行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">负温环境构造资源不足（无温箱/电阻箱）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冰袋/冷柜或传感器模拟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">种 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">故障逐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">bit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">注入能力未确认；与上一版 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">49 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">种状态的范围关系未明确</t>
     </r>
   </si>
@@ -12492,48 +12841,7 @@
     <t xml:space="preserve">AS-14</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仓温传感器短路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">开路时的上报行为未明确（柜温</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">环温已明确上报柜高温告警），是否同样处理需研发确认</t>
-    </r>
+    <t xml:space="preserve">仓温传感器短路/开路时的上报行为未明确（柜温/环温已明确上报柜高温告警），是否同样处理需研发确认</t>
   </si>
 </sst>
 </file>
@@ -12723,7 +13031,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -12809,10 +13117,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13693,7 +13997,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>93</v>
       </c>
@@ -14611,7 +14915,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
         <v>228</v>
       </c>
@@ -14747,7 +15051,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
         <v>248</v>
       </c>
@@ -14815,7 +15119,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
         <v>258</v>
       </c>
@@ -14917,7 +15221,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
         <v>273</v>
       </c>
@@ -14985,7 +15289,7 @@
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
         <v>283</v>
       </c>
@@ -15257,7 +15561,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
         <v>324</v>
       </c>
@@ -16719,19 +17023,19 @@
       <c r="A27" s="17" t="s">
         <v>576</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="16" t="s">
         <v>577</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="16" t="s">
         <v>479</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="16" t="s">
         <v>480</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="16" t="s">
         <v>578</v>
       </c>
     </row>
@@ -16902,16 +17206,16 @@
       <c r="A9" s="17" t="s">
         <v>606</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="16" t="s">
         <v>582</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="16" t="s">
         <v>607</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="16" t="s">
         <v>585</v>
       </c>
     </row>

--- a/JD换电柜终端_20261028提测功能测试用例.xlsx
+++ b/JD换电柜终端_20261028提测功能测试用例.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="609">
   <si>
     <t xml:space="preserve">标题</t>
   </si>
@@ -2670,15 +2670,15 @@
 4. SOC 变化后告警消除，平台状态同步</t>
   </si>
   <si>
-    <t xml:space="preserve">【告警55】-命令电流为 0 且 BMS 充电时 SOC 上升不报</t>
+    <t xml:space="preserve">【告警55】-命令电流=0 且 BMS 充电但 SOC 长期不变，暂停累计不报</t>
   </si>
   <si>
     <t xml:space="preserve">JD_CAB_TER_017</t>
   </si>
   <si>
     <t xml:space="preserve">1. 单仓命令电流置 0
-2. BMS 处于充电状态
-3. 可读取 SOC</t>
+2. BMS 处于充电状态（未禁充）
+3. 可读取 SOC 与累计时长</t>
   </si>
   <si>
     <r>
@@ -2698,26 +2698,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">构造命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
+      <t xml:space="preserve">命令电流置 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
     </r>
     <r>
       <rPr>
@@ -2736,7 +2736,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">充电
+      <t xml:space="preserve">充电中，使 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上升 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">40 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">观察告警
 </t>
     </r>
     <r>
@@ -2775,7 +2832,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">持续上升 </t>
+      <t xml:space="preserve">保持同一数值不变 </t>
     </r>
     <r>
       <rPr>
@@ -2794,7 +2851,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分钟
+      <t xml:space="preserve">分钟 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">观察告警
 </t>
     </r>
     <r>
@@ -2814,13 +2890,54 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">观察告警</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 全程不产生告警 55（SOC 在变化，不满足“30 分钟无变化”）
-2. 平台无 55 记录
-3. 备注：命令电流=0、BMS 充电但 SOC 长期不变 的归属见 AS-13</t>
+      <t xml:space="preserve">记录累计时长是否增长
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">恢复命令电流 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&gt; 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后再观察</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. SOC 上升期间不产生 55（SOC 在变化，不满足“30 分钟无变化”）
+2. SOC 长期不变期间同样不产生 55：该场景属于“命令电流=0 且 BMS 未禁充”，按新增条件暂停累计
+3. 累计时长在置 0 后停止增长，不因 BMS 充电而继续累加
+4. 对照上一版：上版本此场景会累计并报 55，本版本不应再报
+5. 恢复命令电流 &gt; 0 后按 P-08 恢复计时，满 30 分钟有效累计才报</t>
   </si>
   <si>
     <t xml:space="preserve">【告警55】-新增条件：命令电流为 0 且 BMS 未禁充时暂停累计</t>
@@ -4261,7 +4378,7 @@
     <t xml:space="preserve">各仓独立计时并分别上报 55，仓号正确，互不覆盖</t>
   </si>
   <si>
-    <t xml:space="preserve">【告警55】-BMS 故障禁充且命令电流为 0 时的累计归属</t>
+    <t xml:space="preserve">【告警55】-BMS 故障禁充且命令电流为 0 时的累计判定</t>
   </si>
   <si>
     <t xml:space="preserve">JD_CAB_TER_026</t>
@@ -4485,9 +4602,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1. 该场景是否暂停累计按 AS-13 结论判定（禁充与未禁充的边界）
-2. 执行时记录实测行为，作为需求歧义的判定依据
-3. 全程无重复告警、无告警风暴</t>
+    <t xml:space="preserve">1. 暂停条件仅限“命令电流=0 且 BMS 未禁充”，BMS 禁充场景不属于暂停范围，累计应继续，满 30 分钟报 1 条 55
+2. 与 017（未禁充暂停）形成条件互斥对照，两场景结论相反
+3. 全程无重复告警、无告警风暴
+4. 若实测为不报，与已确认规则不符，按需求偏差提交研发</t>
   </si>
   <si>
     <t xml:space="preserve">【告警55】-命令电流由 0 恢复为大于 0 时计时接续与重计</t>
@@ -12506,342 +12624,353 @@
     <t xml:space="preserve">AS-13</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已确认结论：“命令电流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未禁充”一律暂停累计（含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">充电但 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期不变的情形），仅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">禁充时不暂停；上一版“命令电流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">充电继续累计”被本次新增条件覆盖</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_026</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">已关闭，016~029 可判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阻塞</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">broker ACK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丢失</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">延迟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重复的注入或抓取能力缺失</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">需研发/平台支持</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告警 51/54/102 无稳定触发手段（需研发提供触发方式）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未关闭则该组不可执行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">负温环境构造资源不足（无温箱/电阻箱）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冰袋/冷柜或传感器模拟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">故障逐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">bit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">注入能力未确认；与上一版 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">49 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">种状态的范围关系未明确</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">确认工具能力与口径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">判据参数未回填（P-01~P-25），相关用例暂不可判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">见《执行前需回填参数》</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提测前由研发回填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BL-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">满仓功率不足场景的构造手段未确认（P-15/P-25）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺手段则该组只能验证功率充足场景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">待确认</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E55 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中“命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">充电但 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SOC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期不变”的归属：上一版按累计（会报 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），本次新增“命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未禁充暂停”与之重叠，需研发明确优先规则</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_017</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_026</t>
-    </r>
+    <t xml:space="preserve">仓温传感器短路/开路时的上报行为未明确（柜温/环温已明确上报柜高温告警），是否同样处理需研发确认</t>
   </si>
   <si>
     <t xml:space="preserve">影响预期判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阻塞</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">broker ACK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丢失</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">延迟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重复的注入或抓取能力缺失</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">需研发/平台支持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告警 51/54/102 无稳定触发手段（需研发提供触发方式）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未关闭则该组不可执行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">负温环境构造资源不足（无温箱/电阻箱）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冰袋/冷柜或传感器模拟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">种 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">故障逐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">bit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">注入能力未确认；与上一版 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">49 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">种状态的范围关系未明确</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">确认工具能力与口径</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判据参数未回填（P-01~P-25），相关用例暂不可判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">见《执行前需回填参数》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提测前由研发回填</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">满仓功率不足场景的构造手段未确认（P-15/P-25）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">缺手段则该组只能验证功率充足场景</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仓温传感器短路/开路时的上报行为未明确（柜温/环温已明确上报柜高温告警），是否同样处理需研发确认</t>
   </si>
 </sst>
 </file>
@@ -13031,7 +13160,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -13117,6 +13246,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14031,7 +14164,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="330" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
         <v>98</v>
       </c>
@@ -14337,7 +14470,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
         <v>143</v>
       </c>
@@ -17083,131 +17216,131 @@
         <v>476</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="s">
         <v>581</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>582</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="20" t="s">
         <v>583</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="21" t="s">
         <v>584</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>587</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>588</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>566</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>590</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>591</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>496</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>593</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>594</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>518</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>596</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>597</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>561</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>599</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="E7" s="16" t="s">
         <v>601</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>603</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>604</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>534</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>606</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>582</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>607</v>
@@ -17216,7 +17349,7 @@
         <v>199</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/JD换电柜终端_20261028提测功能测试用例.xlsx
+++ b/JD换电柜终端_20261028提测功能测试用例.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="617">
   <si>
     <t xml:space="preserve">标题</t>
   </si>
@@ -2670,7 +2670,7 @@
 4. SOC 变化后告警消除，平台状态同步</t>
   </si>
   <si>
-    <t xml:space="preserve">【告警55】-命令电流=0 且 BMS 充电但 SOC 长期不变，暂停累计不报</t>
+    <t xml:space="preserve">【告警55】-命令电流=0 且 BMS 充电、SOC 上升过程中不报</t>
   </si>
   <si>
     <t xml:space="preserve">JD_CAB_TER_017</t>
@@ -2678,7 +2678,7 @@
   <si>
     <t xml:space="preserve">1. 单仓命令电流置 0
 2. BMS 处于充电状态（未禁充）
-3. 可读取 SOC 与累计时长</t>
+3. 可读取 SOC 与 55 累计时长</t>
   </si>
   <si>
     <r>
@@ -2717,7 +2717,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">，确认 </t>
     </r>
     <r>
       <rPr>
@@ -2736,7 +2736,27 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">充电中，使 </t>
+      <t xml:space="preserve">充电中
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使 </t>
     </r>
     <r>
       <rPr>
@@ -2755,7 +2775,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">上升 </t>
+      <t xml:space="preserve">在 </t>
     </r>
     <r>
       <rPr>
@@ -2774,46 +2794,85 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分钟 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">观察告警
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使 </t>
+      <t xml:space="preserve">分钟内持续上升（每次变化幅度 ≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">观察是否产生 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，并记录累计时长变化
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">停止 </t>
     </r>
     <r>
       <rPr>
@@ -2832,112 +2891,52 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">保持同一数值不变 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">40 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分钟 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">观察告警
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">记录累计时长是否增长
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">恢复命令电流 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">&gt; 0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后再观察</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1. SOC 上升期间不产生 55（SOC 在变化，不满足“30 分钟无变化”）
-2. SOC 长期不变期间同样不产生 55：该场景属于“命令电流=0 且 BMS 未禁充”，按新增条件暂停累计
-3. 累计时长在置 0 后停止增长，不因 BMS 充电而继续累加
-4. 对照上一版：上版本此场景会累计并报 55，本版本不应再报
-5. 恢复命令电流 &gt; 0 后按 P-08 恢复计时，满 30 分钟有效累计才报</t>
+      <t xml:space="preserve">变化后观察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟（该分支见 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_078</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. SOC 持续上升期间不产生 55：SOC 在变化，不满足“30 分钟无变化”
+2. 每次 SOC 变化后累计时长归零
+3. 累计时长不因 BMS 充电而继续累加（处于暂停条件）
+4. 41 分钟内无重复告警、无延时告警</t>
   </si>
   <si>
     <t xml:space="preserve">【告警55】-新增条件：命令电流为 0 且 BMS 未禁充时暂停累计</t>
@@ -11524,6 +11523,359 @@
 2. 平台最终状态与终端一致，且无重复告警</t>
   </si>
   <si>
+    <t xml:space="preserve">【告警55】-命令电流=0 且 BMS 充电但 SOC 长期不变，暂停累计不报（专项）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_CAB_TER_078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29 10:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 单仓可独立控制命令电流
+2. 可读取 BMS 充电状态与禁充状态（P-24 字段）
+3. 可读取 SOC 与 55 累计时长
+4. 本版本固件；上一版固件可复测以做对照</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">选单仓，命令电流置 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，确认 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">BMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">处于充电状态且未禁充
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟保持同一数值不变，观察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟节点
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">继续保持不变至满 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟，观察是否产生 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">55
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">继续保持不变至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">40 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟，观察是否产生 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">55 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">及累计时长是否增长
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">恢复命令电流 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&gt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">SOC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保持不变 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟，观察是否产生 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">55
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用上一版固件复测同场景并记录结果</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 25 分钟节点不产生 55（未满 30 分钟）
+2. 满 30 分钟仍不产生 55：命令电流=0 且 BMS 未禁充属于暂停累计条件
+3. 40 分钟仍不产生 55，无重复上报、无延时补报
+4. 累计时长自命令电流置 0 起停止增长，不因 BMS 充电而累加
+5. 恢复命令电流 &gt; 0 后按 P-08 重新计时，满 30 分钟有效累计才报 1 条 55
+6. 与上一版对照：上一版该场景会累计并报 55，本版本不报，结论存证</t>
+  </si>
+  <si>
     <t xml:space="preserve">批次</t>
   </si>
   <si>
@@ -11595,6 +11947,99 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">集合、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_078</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BL-02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关闭，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P-05~P-07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已回填</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">078 为告警55 暂停条件专项，与 AS-13 结论配套</t>
+  </si>
+  <si>
+    <t xml:space="preserve">批次三</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次新增 P1/P2（边界与异常）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_001~JD_CAB_TER_054 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P1/P2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">集合</t>
     </r>
   </si>
@@ -11606,6 +12051,351 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">P-08~P-18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已回填</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">无</t>
+  </si>
+  <si>
+    <t xml:space="preserve">批次四</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阻塞解除后回补（负温组 + broker ACK）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_030~JD_CAB_TER_036</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_077</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BL-01~BL-04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关闭</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">回归引用对照（本次编号 → 上一版历史编号）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上一版历史编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_039/044）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_045）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_046）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_047/048）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_052/056）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_058）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_052/054）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_066/067/068）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_073/080）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_079）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_076）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_084）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_085）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_001~038）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_073）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_086）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD_BMS_OTA_162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_085，Blocked）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_088）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_089）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（回归 JD_BMS_OTA_090/092）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参数/判据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关联用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">责任方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物模型目标版本号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">研发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待回填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未回填则版本校验无法判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电池升级包版本号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未回填则升级结果无法核对</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电池丢失判定后上报的告警/事件码及 SN 字段名</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">001~007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">003</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本次判定形式为 SN 为空 + 告警/事件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次检测总时长与单次采样间隔</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">001~007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已确认</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需求已明确：5 次检测、时长 5-6s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告警 51/54/102 的触发/恢复条件与触发手段</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">008~015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">055</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">BL-02 </t>
     </r>
     <r>
@@ -11614,8 +12404,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">关闭，</t>
-    </r>
+      <t xml:space="preserve">未关闭前该组不可执行</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程升级种类与升级窗口起止定义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">四类：apk、仓控板、消防板、电池</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抑制期间本地行为范围（指示灯/蜂鸣/停充）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">008~015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前按“仅不上报平台”设计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-08</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -11623,7 +12439,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P-05~P-07 </t>
+      <t xml:space="preserve">E55 </t>
     </r>
     <r>
       <rPr>
@@ -11631,19 +12447,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已回填</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">无</t>
-  </si>
-  <si>
-    <t xml:space="preserve">批次三</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本次新增 P1/P2（边界与异常）</t>
-  </si>
-  <si>
+      <t xml:space="preserve">计时起点、暂停恢复后接续或重计、</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -11651,7 +12456,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">JD_CAB_TER_001~JD_CAB_TER_054 </t>
+      <t xml:space="preserve">SOC </t>
     </r>
     <r>
       <rPr>
@@ -11659,8 +12464,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中的 </t>
-    </r>
+      <t xml:space="preserve">变化清零规则</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">016~029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">决定 30 分钟计时语义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告警 55 与换电阈值的关系（掉电且 SOC 高于阈值）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需与上一版用例对齐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">换电阈值数值与 95-100 / 0-95 区间口径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">060~064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响上升/下降判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温度编码位宽、量程（-40~100℃）、精度与允许误差</t>
+  </si>
+  <si>
+    <t xml:space="preserve">030~038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">量程 -40~100℃，按 int8、1℃ 设计；短路/开路见 P-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低温告警阈值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">负温告警的判定依据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">满需求电流值与允许容差</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -11668,7 +12529,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P1/P2 </t>
+      <t xml:space="preserve">039</t>
     </r>
     <r>
       <rPr>
@@ -11676,10 +12537,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">集合</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">、</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -11687,36 +12546,116 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P-08~P-18 </t>
-    </r>
+      <t xml:space="preserve">043</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">研发/硬件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">满需求验收判据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保底涓流电流值</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已回填</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">批次四</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阻塞解除后回补（负温组 + broker ACK）</t>
-  </si>
-  <si>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">039</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">JD_CAB_TER_030~JD_CAB_TER_036</t>
-    </r>
+      <t xml:space="preserve">040</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">“涓流活保”的取值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柜总功率上限与“总功率不足”构造方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">039~042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">满仓限功率场景的构造依据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">升级关键 4 步定义、重试间隔与总超时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">045~047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失败步定位依据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">升级中断电/断网后的断点与恢复策略</t>
+  </si>
+  <si>
+    <t xml:space="preserve">断点续传或重来</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重连最小间隔、最大重试次数、退避上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">051~054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">网络优化验收指标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">门磁状态上报时延、告警消除上报时延</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">056</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -11729,8 +12668,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">JD_CAB_TER_077</t>
-    </r>
+      <t xml:space="preserve">063</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">时延类判据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">业务窗口起止定义与定时上报周期</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070~072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">静默范围判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-21</t>
   </si>
   <si>
     <r>
@@ -11740,7 +12697,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BL-01~BL-04 </t>
+      <t xml:space="preserve">JD </t>
     </r>
     <r>
       <rPr>
@@ -11748,184 +12705,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">关闭</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">回归引用对照（本次编号 → 上一版历史编号）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本次编号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上一版历史编号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">说明</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_039/044）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_045）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_046）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_047/048）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_052/056）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_058）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_052/054）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_066/067/068）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_073/080）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_079）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_076）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_084）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_085）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_001~038）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_073）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_086）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JD_BMS_OTA_162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_085，Blocked）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_088）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_089）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（回归 JD_BMS_OTA_090/092）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参数/判据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关联用例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">责任方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状态</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物模型目标版本号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">研发</t>
-  </si>
-  <si>
-    <t xml:space="preserve">待回填</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未回填则版本校验无法判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">电池升级包版本号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未回填则升级结果无法核对</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">电池丢失判定后上报的告警/事件码及 SN 字段名</t>
-  </si>
-  <si>
+      <t xml:space="preserve">国标电池 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -11933,7 +12714,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">001~007</t>
+      <t xml:space="preserve">SN </t>
     </r>
     <r>
       <rPr>
@@ -11941,6 +12722,53 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">格式、长度与字符集</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">研发/电池厂家</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校验依据</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逐 bit 注入能力；上一版 49 种状态与本版 22 种的范围关系</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">065</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">、</t>
     </r>
     <r>
@@ -11950,14 +12778,11 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">003</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本次判定形式为 SN 为空 + 告警/事件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-04</t>
+      <t xml:space="preserve">075</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">研发/测试</t>
   </si>
   <si>
     <r>
@@ -11967,7 +12792,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5 </t>
+      <t xml:space="preserve">BL-04</t>
     </r>
     <r>
       <rPr>
@@ -11975,23 +12800,14 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">次检测总时长与单次采样间隔</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">001~007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">需求已明确：5 次检测、时长 5-6s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告警 51/54/102 的触发/恢复条件与触发手段</t>
+      <t xml:space="preserve">；避免范围口径不一致漏测</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告警上报/消除的重试策略（次数、间隔、幂等）</t>
   </si>
   <si>
     <r>
@@ -12001,7 +12817,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">008~015</t>
+      <t xml:space="preserve">068</t>
     </r>
     <r>
       <rPr>
@@ -12018,61 +12834,57 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">055</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">069</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BL-02 </t>
-    </r>
+      <t xml:space="preserve">077</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未关闭前该组不可执行</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">远程升级种类与升级窗口起止定义</t>
-  </si>
-  <si>
-    <t xml:space="preserve">四类：apk、仓控板、消防板、电池</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">抑制期间本地行为范围（指示灯/蜂鸣/停充）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008~015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目前按“仅不上报平台”设计</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-08</t>
-  </si>
-  <si>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ACK </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">确认机制判据</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P-24</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">E55 </t>
+      <t xml:space="preserve">BMS </t>
     </r>
     <r>
       <rPr>
@@ -12080,8 +12892,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">计时起点、暂停恢复后接续或重计、</t>
-    </r>
+      <t xml:space="preserve">禁充状态的判定字段与取值</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -12089,7 +12903,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">SOC </t>
+      <t xml:space="preserve">018</t>
     </r>
     <r>
       <rPr>
@@ -12097,64 +12911,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">变化清零规则</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">016~029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">决定 30 分钟计时语义</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告警 55 与换电阈值的关系（掉电且 SOC 高于阈值）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">需与上一版用例对齐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">换电阈值数值与 95-100 / 0-95 区间口径</t>
-  </si>
-  <si>
-    <t xml:space="preserve">060~064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响上升/下降判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温度编码位宽、量程（-40~100℃）、精度与允许误差</t>
-  </si>
-  <si>
-    <t xml:space="preserve">030~038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">量程 -40~100℃，按 int8、1℃ 设计；短路/开路见 P-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">低温告警阈值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">负温告警的判定依据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">满需求电流值与允许容差</t>
-  </si>
-  <si>
+      <t xml:space="preserve">、</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -12162,7 +12920,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">039</t>
+      <t xml:space="preserve">019</t>
     </r>
     <r>
       <rPr>
@@ -12179,34 +12937,75 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">043</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">研发/硬件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">满需求验收判据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保底涓流电流值</t>
-  </si>
-  <si>
+      <t xml:space="preserve">026</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">039</t>
-    </r>
+      <t xml:space="preserve">028</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">新增 E55 暂停条件依赖该字段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">满仓充电场景构造方式（全仓有电池、并发充电）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试/研发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺陷回归场景的复现条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柜温/环温短路与开路时上报的“柜高温告警”告警码及温度上报值定义</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次改为有符号数后短路/开路上报柜高温告警</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已确认结论：“命令电流=0 且 BMS 未禁充”一律暂停累计（含 BMS 充电但 SOC 长期不变的情形），仅 BMS 禁充时不暂停；上一版“命令电流=0 且 BMS 充电继续累计”被本次新增条件覆盖</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JD_CAB_TER_017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -12219,565 +13018,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">040</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">“涓流活保”的取值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柜总功率上限与“总功率不足”构造方式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">039~042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">满仓限功率场景的构造依据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">升级关键 4 步定义、重试间隔与总超时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">045~047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">失败步定位依据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">升级中断电/断网后的断点与恢复策略</t>
-  </si>
-  <si>
-    <t xml:space="preserve">断点续传或重来</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重连最小间隔、最大重试次数、退避上限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">051~054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">网络优化验收指标</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">门磁状态上报时延、告警消除上报时延</t>
-  </si>
-  <si>
+      <t xml:space="preserve">JD_CAB_TER_026</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="宋体"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">056</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">063</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">时延类判据</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">业务窗口起止定义与定时上报周期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070~072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">静默范围判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-21</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">国标电池 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">格式、长度与字符集</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">研发/电池厂家</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">校验依据</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逐 bit 注入能力；上一版 49 种状态与本版 22 种的范围关系</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">065</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">075</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">研发/测试</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BL-04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；避免范围口径不一致漏测</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告警上报/消除的重试策略（次数、间隔、幂等）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">068</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">069</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">077</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ACK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">确认机制判据</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P-24</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">禁充状态的判定字段与取值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">018</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">028</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">新增 E55 暂停条件依赖该字段</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">满仓充电场景构造方式（全仓有电池、并发充电）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">测试/研发</t>
-  </si>
-  <si>
-    <t xml:space="preserve">缺陷回归场景的复现条件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柜温/环温短路与开路时上报的“柜高温告警”告警码及温度上报值定义</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本次改为有符号数后短路/开路上报柜高温告警</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事项</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响用例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS-13</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已确认结论：“命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未禁充”一律暂停累计（含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">充电但 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SOC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期不变的情形），仅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">禁充时不暂停；上一版“命令电流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BMS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">充电继续累计”被本次新增条件覆盖</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_017</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JD_CAB_TER_026</t>
+      <t xml:space="preserve">JD_CAB_TER_078</t>
     </r>
   </si>
   <si>
@@ -13160,7 +13418,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -13246,10 +13504,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13567,7 +13821,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.37"/>
@@ -14164,7 +14418,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="330" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
         <v>98</v>
       </c>
@@ -16237,6 +16491,40 @@
       </c>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L78"/>
@@ -16269,118 +16557,118 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>21</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D3" s="17" t="n">
-        <v>15</v>
+        <v>424</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>425</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>40</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16388,10 +16676,10 @@
         <v>294</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16399,10 +16687,10 @@
         <v>300</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16410,10 +16698,10 @@
         <v>305</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16421,10 +16709,10 @@
         <v>310</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16432,10 +16720,10 @@
         <v>315</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16443,10 +16731,10 @@
         <v>320</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16454,10 +16742,10 @@
         <v>325</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16465,10 +16753,10 @@
         <v>330</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16476,10 +16764,10 @@
         <v>340</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16487,10 +16775,10 @@
         <v>345</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16498,10 +16786,10 @@
         <v>350</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16509,10 +16797,10 @@
         <v>355</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16520,10 +16808,10 @@
         <v>360</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16531,10 +16819,10 @@
         <v>380</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16542,10 +16830,10 @@
         <v>390</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16553,10 +16841,10 @@
         <v>395</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16564,10 +16852,10 @@
         <v>400</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16575,10 +16863,10 @@
         <v>365</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16586,10 +16874,10 @@
         <v>370</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16597,10 +16885,10 @@
         <v>375</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -16637,539 +16925,539 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>310</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>380</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>479</v>
-      </c>
       <c r="E4" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>335</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>189</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>526</v>
-      </c>
       <c r="E16" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>385</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>199</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -17207,149 +17495,149 @@
         <v>10</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>582</v>
+        <v>500</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>590</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>199</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
